--- a/hardware/bom/MR2_Reactive_LEDs_System_BOM.xlsx
+++ b/hardware/bom/MR2_Reactive_LEDs_System_BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kilian\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d753a926efe4f701/Documents/GitHub/mr2-reactive-leds/hardware/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFBE3A61-E2F0-4606-A7D7-39BA249C67FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{AFBE3A61-E2F0-4606-A7D7-39BA249C67FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEAA20C5-125B-49F7-979C-B9750F47E647}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9AADAE85-9F9F-49F2-B772-A5236C2D1725}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="83">
   <si>
     <t>Category</t>
   </si>
@@ -65,60 +65,27 @@
     <t>Main microcontroller</t>
   </si>
   <si>
-    <t>Runs reactive LED firmware</t>
-  </si>
-  <si>
     <t>Sensor</t>
   </si>
   <si>
-    <t>Vehicle motion sensing</t>
-  </si>
-  <si>
-    <t>Detects acceleration, braking and cornering</t>
-  </si>
-  <si>
     <t>Lighting</t>
   </si>
   <si>
-    <t>Logic</t>
-  </si>
-  <si>
-    <t>3.3V to 5V data conversion</t>
-  </si>
-  <si>
     <t>Control</t>
   </si>
   <si>
     <t>Power</t>
   </si>
   <si>
-    <t>Vehicle power conversion</t>
-  </si>
-  <si>
     <t>Protection</t>
   </si>
   <si>
-    <t>Switch</t>
-  </si>
-  <si>
     <t>Gebildet Metal Toggle Switch</t>
   </si>
   <si>
     <t>Connectors</t>
   </si>
   <si>
-    <t>Wiring</t>
-  </si>
-  <si>
-    <t>Various</t>
-  </si>
-  <si>
-    <t>Main power wiring</t>
-  </si>
-  <si>
-    <t>Signal wiring</t>
-  </si>
-  <si>
     <t>PCB</t>
   </si>
   <si>
@@ -128,154 +95,199 @@
     <t>Supplier / Source</t>
   </si>
   <si>
-    <t>MPU6050 / GY-521 Accelerometer</t>
-  </si>
-  <si>
-    <t>WS2812B Addressable LED Strip</t>
-  </si>
-  <si>
-    <t>2 × 1m</t>
-  </si>
-  <si>
-    <t>Interior footwell lighting</t>
-  </si>
-  <si>
-    <t>Left and right independent outputs</t>
-  </si>
-  <si>
-    <t>SN74AHCT125N Level Shifter</t>
-  </si>
-  <si>
-    <t>Improves WS2812B reliability</t>
-  </si>
-  <si>
-    <t>Rotary Encoder</t>
-  </si>
-  <si>
-    <t>User input</t>
-  </si>
-  <si>
-    <t>Brightness adjustment and mode selection</t>
-  </si>
-  <si>
-    <t>Master power control</t>
-  </si>
-  <si>
-    <t>Complete system shutdown</t>
-  </si>
-  <si>
-    <t>Main controller board</t>
-  </si>
-  <si>
-    <t>Manufactured by JLCPCB</t>
-  </si>
-  <si>
-    <t>12V to 5V Buck Converter</t>
-  </si>
-  <si>
-    <t>Provides regulated 5V supply</t>
-  </si>
-  <si>
     <t>Inline Fuse Holder</t>
   </si>
   <si>
-    <t>Electrical protection</t>
-  </si>
-  <si>
-    <t>Installed on vehicle power feed</t>
-  </si>
-  <si>
-    <t>Blade Fuse</t>
-  </si>
-  <si>
     <t>Overcurrent protection</t>
   </si>
   <si>
-    <t>Fuse rating to be confirmed</t>
-  </si>
-  <si>
-    <t>JST-XH Connector Kit</t>
-  </si>
-  <si>
-    <t>Removable PCB wiring</t>
-  </si>
-  <si>
-    <t>External component connections</t>
-  </si>
-  <si>
-    <t>18AWG Red Wire</t>
-  </si>
-  <si>
-    <t>Length</t>
-  </si>
-  <si>
-    <t>Vehicle power supply</t>
-  </si>
-  <si>
-    <t>18AWG Black Wire</t>
-  </si>
-  <si>
-    <t>Ground wiring</t>
-  </si>
-  <si>
-    <t>Vehicle ground return</t>
-  </si>
-  <si>
-    <t>24AWG Assorted Wire</t>
-  </si>
-  <si>
-    <t>Sensor and control connections</t>
-  </si>
-  <si>
-    <t>Heat Shrink Tubing</t>
-  </si>
-  <si>
-    <t>Insulation</t>
-  </si>
-  <si>
-    <t>Protects solder joints</t>
-  </si>
-  <si>
-    <t>Mounting</t>
-  </si>
-  <si>
     <t>VHB Mounting Tape</t>
   </si>
   <si>
-    <t>Component mounting</t>
-  </si>
-  <si>
-    <t>LED and sensor mounting</t>
-  </si>
-  <si>
-    <t>Cable Ties</t>
-  </si>
-  <si>
-    <t>Cable management</t>
-  </si>
-  <si>
-    <t>Wiring organisation</t>
-  </si>
-  <si>
     <t>Enclosure</t>
   </si>
   <si>
-    <t>Control Box</t>
-  </si>
-  <si>
-    <t>Protects electronics</t>
-  </si>
-  <si>
-    <t>Final enclosure to be selected</t>
-  </si>
-  <si>
-    <t>Cable Glands</t>
-  </si>
-  <si>
-    <t>Cable protection</t>
-  </si>
-  <si>
-    <t>Added during final assembly</t>
+    <t>Development board</t>
+  </si>
+  <si>
+    <t>MPU6050 / GY-521</t>
+  </si>
+  <si>
+    <t>Acceleration and G-force sensing</t>
+  </si>
+  <si>
+    <t>Chassis-mounted</t>
+  </si>
+  <si>
+    <t>WS2812B LED strip</t>
+  </si>
+  <si>
+    <t>2 × 1 m</t>
+  </si>
+  <si>
+    <t>Reactive interior lighting</t>
+  </si>
+  <si>
+    <t>Left and right sides</t>
+  </si>
+  <si>
+    <t>Level Shifting</t>
+  </si>
+  <si>
+    <t>SN74AHCT125N</t>
+  </si>
+  <si>
+    <t>3.3 V to 5 V LED data level shifting</t>
+  </si>
+  <si>
+    <t>5 V logic supply</t>
+  </si>
+  <si>
+    <t>KY-040 Rotary Encoder</t>
+  </si>
+  <si>
+    <t>Brightness and lighting mode control</t>
+  </si>
+  <si>
+    <t>Includes push button</t>
+  </si>
+  <si>
+    <t>12 V to 5 V Buck Converter</t>
+  </si>
+  <si>
+    <t>Converts vehicle 12 V supply to regulated 5 V</t>
+  </si>
+  <si>
+    <t>Protects added vehicle wiring</t>
+  </si>
+  <si>
+    <t>Installed close to 12 V supply tap</t>
+  </si>
+  <si>
+    <t>Fuse</t>
+  </si>
+  <si>
+    <t>Power Connection</t>
+  </si>
+  <si>
+    <t>2-pin Waterproof Automotive Connector</t>
+  </si>
+  <si>
+    <t>1 pair</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Removable 12 V connection to buck converter</t>
+  </si>
+  <si>
+    <t>Wire-to-wire connection</t>
+  </si>
+  <si>
+    <t>Switching</t>
+  </si>
+  <si>
+    <t>Main system power switch</t>
+  </si>
+  <si>
+    <t>JST-XH 2.54 mm Connector Kit</t>
+  </si>
+  <si>
+    <t>1 kit</t>
+  </si>
+  <si>
+    <t>Removable PCB connections</t>
+  </si>
+  <si>
+    <t>Sensors, encoder and LED connections</t>
+  </si>
+  <si>
+    <t>Wire</t>
+  </si>
+  <si>
+    <t>18 AWG Red/Black Automotive Wire</t>
+  </si>
+  <si>
+    <t>As required</t>
+  </si>
+  <si>
+    <t>12 V and high-current power wiring</t>
+  </si>
+  <si>
+    <t>Red = positive, black = ground</t>
+  </si>
+  <si>
+    <t>Low-current signal wiring</t>
+  </si>
+  <si>
+    <t>Various colours for identification</t>
+  </si>
+  <si>
+    <t>JLCPCB</t>
+  </si>
+  <si>
+    <t>Main circuit board</t>
+  </si>
+  <si>
+    <t>Custom-designed two-layer PCB</t>
+  </si>
+  <si>
+    <t>Hardware</t>
+  </si>
+  <si>
+    <t>Mounting LED strips and components</t>
+  </si>
+  <si>
+    <t>Automotive-grade adhesive</t>
+  </si>
+  <si>
+    <t>Control Box / Project Enclosure</t>
+  </si>
+  <si>
+    <t>Houses PCB and electronics</t>
+  </si>
+  <si>
+    <t>Hidden behind centre dash</t>
+  </si>
+  <si>
+    <t>Capacitor</t>
+  </si>
+  <si>
+    <t>Decoupling Capacitors</t>
+  </si>
+  <si>
+    <t>Power supply filtering</t>
+  </si>
+  <si>
+    <t>Mounted on custom PCB</t>
+  </si>
+  <si>
+    <t>Resistor</t>
+  </si>
+  <si>
+    <t>330 Ω Resistor</t>
+  </si>
+  <si>
+    <t>WS2812B data-line protection</t>
+  </si>
+  <si>
+    <t>Placed in series with LED data signal</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>Powers controller</t>
+  </si>
+  <si>
+    <t>15A</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>24 AWG Wire</t>
   </si>
 </sst>
 </file>
@@ -319,13 +331,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -342,6 +360,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -661,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E2E7EC-100C-4E0A-AAC5-766FAA06E1AD}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
@@ -678,11 +700,11 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -691,161 +713,179 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>1</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="2">
+    </row>
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3">
         <v>1</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="2">
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3">
         <v>1</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="D8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="3">
         <v>1</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
         <v>46</v>
       </c>
@@ -853,35 +893,39 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="2">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="2">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>52</v>
       </c>
@@ -889,150 +933,140 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E15" s="2" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>23</v>
+        <v>67</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
+    </row>
+    <row r="20" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/hardware/bom/MR2_Reactive_LEDs_System_BOM.xlsx
+++ b/hardware/bom/MR2_Reactive_LEDs_System_BOM.xlsx
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Not yet purchased</t>
+          <t>Not purchased — decided not to pursue</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Planned fix, not yet installed — see build log "USB Power Backfeed Discovered"</t>
+          <t>Would fix a known minor USB-power backfeed issue, but impact judged too small to be worth it — see build log</t>
         </is>
       </c>
     </row>
